--- a/datos/valido_uA_mV.xlsx
+++ b/datos/valido_uA_mV.xlsx
@@ -433,7 +433,7 @@
         <v>-1</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.455870697873276e-07</v>
+        <v>-5.176492041818887e-07</v>
       </c>
     </row>
     <row r="3">
@@ -441,7 +441,7 @@
         <v>-0.9797979797979798</v>
       </c>
       <c r="B3" t="n">
-        <v>-4.361452291255878e-07</v>
+        <v>-4.389874124475519e-07</v>
       </c>
     </row>
     <row r="4">
@@ -449,7 +449,7 @@
         <v>-0.9595959595959596</v>
       </c>
       <c r="B4" t="n">
-        <v>-5.292612126163223e-07</v>
+        <v>-5.647252093437225e-07</v>
       </c>
     </row>
     <row r="5">
@@ -457,7 +457,7 @@
         <v>-0.9393939393939394</v>
       </c>
       <c r="B5" t="n">
-        <v>-4.541860497520617e-07</v>
+        <v>-5.85299352012887e-07</v>
       </c>
     </row>
     <row r="6">
@@ -465,7 +465,7 @@
         <v>-0.9191919191919192</v>
       </c>
       <c r="B6" t="n">
-        <v>-4.679908825296195e-07</v>
+        <v>-5.809535670103779e-07</v>
       </c>
     </row>
     <row r="7">
@@ -473,7 +473,7 @@
         <v>-0.898989898989899</v>
       </c>
       <c r="B7" t="n">
-        <v>-5.411090941020911e-07</v>
+        <v>-5.156891664575949e-07</v>
       </c>
     </row>
     <row r="8">
@@ -481,7 +481,7 @@
         <v>-0.8787878787878788</v>
       </c>
       <c r="B8" t="n">
-        <v>-4.104382560735903e-07</v>
+        <v>-4.490279172474666e-07</v>
       </c>
     </row>
     <row r="9">
@@ -489,7 +489,7 @@
         <v>-0.8585858585858586</v>
       </c>
       <c r="B9" t="n">
-        <v>-4.982005175422342e-07</v>
+        <v>-4.706890576087513e-07</v>
       </c>
     </row>
     <row r="10">
@@ -497,7 +497,7 @@
         <v>-0.8383838383838383</v>
       </c>
       <c r="B10" t="n">
-        <v>-4.770701307768806e-07</v>
+        <v>-4.479213625227671e-07</v>
       </c>
     </row>
     <row r="11">
@@ -505,7 +505,7 @@
         <v>-0.8181818181818181</v>
       </c>
       <c r="B11" t="n">
-        <v>-5.27872279540781e-07</v>
+        <v>-4.618398690318095e-07</v>
       </c>
     </row>
     <row r="12">
@@ -513,7 +513,7 @@
         <v>-0.797979797979798</v>
       </c>
       <c r="B12" t="n">
-        <v>-5.494521297579448e-07</v>
+        <v>-5.089402919892034e-07</v>
       </c>
     </row>
     <row r="13">
@@ -521,7 +521,7 @@
         <v>-0.7777777777777778</v>
       </c>
       <c r="B13" t="n">
-        <v>-4.340444276592008e-07</v>
+        <v>-5.014288326622062e-07</v>
       </c>
     </row>
     <row r="14">
@@ -529,7 +529,7 @@
         <v>-0.7575757575757576</v>
       </c>
       <c r="B14" t="n">
-        <v>-5.172607530609052e-07</v>
+        <v>-4.679261174936258e-07</v>
       </c>
     </row>
     <row r="15">
@@ -537,7 +537,7 @@
         <v>-0.7373737373737373</v>
       </c>
       <c r="B15" t="n">
-        <v>-5.711139978059375e-07</v>
+        <v>-4.42349849801832e-07</v>
       </c>
     </row>
     <row r="16">
@@ -545,7 +545,7 @@
         <v>-0.7171717171717171</v>
       </c>
       <c r="B16" t="n">
-        <v>-5.295248292095708e-07</v>
+        <v>-5.283606394601131e-07</v>
       </c>
     </row>
     <row r="17">
@@ -553,7 +553,7 @@
         <v>-0.696969696969697</v>
       </c>
       <c r="B17" t="n">
-        <v>-4.311881254698522e-07</v>
+        <v>-5.181032263927268e-07</v>
       </c>
     </row>
     <row r="18">
@@ -561,7 +561,7 @@
         <v>-0.6767676767676767</v>
       </c>
       <c r="B18" t="n">
-        <v>-4.666084900702412e-07</v>
+        <v>-4.868728400727183e-07</v>
       </c>
     </row>
     <row r="19">
@@ -569,7 +569,7 @@
         <v>-0.6565656565656566</v>
       </c>
       <c r="B19" t="n">
-        <v>-3.945505289415197e-07</v>
+        <v>-6.024467961350137e-07</v>
       </c>
     </row>
     <row r="20">
@@ -577,7 +577,7 @@
         <v>-0.6363636363636364</v>
       </c>
       <c r="B20" t="n">
-        <v>-5.032693500571449e-07</v>
+        <v>-4.654944744157926e-07</v>
       </c>
     </row>
     <row r="21">
@@ -585,7 +585,7 @@
         <v>-0.6161616161616161</v>
       </c>
       <c r="B21" t="n">
-        <v>-4.355036358197664e-07</v>
+        <v>-4.589624648089605e-07</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>-0.5959595959595959</v>
       </c>
       <c r="B22" t="n">
-        <v>-5.070677015843398e-07</v>
+        <v>-4.643786253700058e-07</v>
       </c>
     </row>
     <row r="23">
@@ -601,7 +601,7 @@
         <v>-0.5757575757575757</v>
       </c>
       <c r="B23" t="n">
-        <v>-5.614873074096724e-07</v>
+        <v>-4.564197452386764e-07</v>
       </c>
     </row>
     <row r="24">
@@ -609,7 +609,7 @@
         <v>-0.5555555555555556</v>
       </c>
       <c r="B24" t="n">
-        <v>-5.086221919773332e-07</v>
+        <v>-5.419908513893661e-07</v>
       </c>
     </row>
     <row r="25">
@@ -617,7 +617,7 @@
         <v>-0.5353535353535352</v>
       </c>
       <c r="B25" t="n">
-        <v>-5.70566977694847e-07</v>
+        <v>-4.977315549626457e-07</v>
       </c>
     </row>
     <row r="26">
@@ -625,7 +625,7 @@
         <v>-0.5151515151515151</v>
       </c>
       <c r="B26" t="n">
-        <v>-5.909848449040529e-07</v>
+        <v>-4.673231876594135e-07</v>
       </c>
     </row>
     <row r="27">
@@ -633,7 +633,7 @@
         <v>-0.4949494949494949</v>
       </c>
       <c r="B27" t="n">
-        <v>-4.845057607263355e-07</v>
+        <v>-4.560147793322681e-07</v>
       </c>
     </row>
     <row r="28">
@@ -641,7 +641,7 @@
         <v>-0.4747474747474747</v>
       </c>
       <c r="B28" t="n">
-        <v>-5.011207763717006e-07</v>
+        <v>-4.943562074595324e-07</v>
       </c>
     </row>
     <row r="29">
@@ -649,7 +649,7 @@
         <v>-0.4545454545454545</v>
       </c>
       <c r="B29" t="n">
-        <v>-5.779837810384028e-07</v>
+        <v>-5.555109746110451e-07</v>
       </c>
     </row>
     <row r="30">
@@ -657,7 +657,7 @@
         <v>-0.4343434343434343</v>
       </c>
       <c r="B30" t="n">
-        <v>-4.329382284374694e-07</v>
+        <v>-5.280703802390346e-07</v>
       </c>
     </row>
     <row r="31">
@@ -665,7 +665,7 @@
         <v>-0.4141414141414141</v>
       </c>
       <c r="B31" t="n">
-        <v>-4.6257037672129e-07</v>
+        <v>-4.756273001273253e-07</v>
       </c>
     </row>
     <row r="32">
@@ -673,7 +673,7 @@
         <v>-0.3939393939393939</v>
       </c>
       <c r="B32" t="n">
-        <v>-4.552879775097201e-07</v>
+        <v>-5.194424025494453e-07</v>
       </c>
     </row>
     <row r="33">
@@ -681,7 +681,7 @@
         <v>-0.3737373737373737</v>
       </c>
       <c r="B33" t="n">
-        <v>-5.074609550671582e-07</v>
+        <v>-4.767034262816237e-07</v>
       </c>
     </row>
     <row r="34">
@@ -689,7 +689,7 @@
         <v>-0.3535353535353535</v>
       </c>
       <c r="B34" t="n">
-        <v>-5.551727349236285e-07</v>
+        <v>-4.622545389507718e-07</v>
       </c>
     </row>
     <row r="35">
@@ -697,7 +697,7 @@
         <v>-0.3333333333333333</v>
       </c>
       <c r="B35" t="n">
-        <v>-4.983331700153261e-07</v>
+        <v>-4.836521320695332e-07</v>
       </c>
     </row>
     <row r="36">
@@ -705,7 +705,7 @@
         <v>-0.313131313131313</v>
       </c>
       <c r="B36" t="n">
-        <v>-5.456264701207519e-07</v>
+        <v>-5.529235736238256e-07</v>
       </c>
     </row>
     <row r="37">
@@ -713,7 +713,7 @@
         <v>-0.2929292929292928</v>
       </c>
       <c r="B37" t="n">
-        <v>-4.818824583124874e-07</v>
+        <v>-4.73194569236108e-07</v>
       </c>
     </row>
     <row r="38">
@@ -721,7 +721,7 @@
         <v>-0.2727272727272727</v>
       </c>
       <c r="B38" t="n">
-        <v>-4.873214727153368e-07</v>
+        <v>-4.506339267283381e-07</v>
       </c>
     </row>
     <row r="39">
@@ -729,7 +729,7 @@
         <v>-0.2525252525252525</v>
       </c>
       <c r="B39" t="n">
-        <v>-4.068899809251399e-07</v>
+        <v>-5.901894209931789e-07</v>
       </c>
     </row>
     <row r="40">
@@ -737,7 +737,7 @@
         <v>-0.2323232323232323</v>
       </c>
       <c r="B40" t="n">
-        <v>-4.185106239210362e-07</v>
+        <v>-4.911611832080171e-07</v>
       </c>
     </row>
     <row r="41">
@@ -745,7 +745,7 @@
         <v>-0.212121212121212</v>
       </c>
       <c r="B41" t="n">
-        <v>-4.370017808517054e-07</v>
+        <v>-4.865140525470511e-07</v>
       </c>
     </row>
     <row r="42">
@@ -753,7 +753,7 @@
         <v>-0.1919191919191918</v>
       </c>
       <c r="B42" t="n">
-        <v>-3.717077790873355e-07</v>
+        <v>-4.71291067338697e-07</v>
       </c>
     </row>
     <row r="43">
@@ -761,7 +761,7 @@
         <v>-0.1717171717171716</v>
       </c>
       <c r="B43" t="n">
-        <v>-3.960197133652501e-07</v>
+        <v>-3.786554226942276e-07</v>
       </c>
     </row>
     <row r="44">
@@ -769,7 +769,7 @@
         <v>-0.1515151515151515</v>
       </c>
       <c r="B44" t="n">
-        <v>-3.847197362505444e-07</v>
+        <v>-3.359830326826454e-07</v>
       </c>
     </row>
     <row r="45">
@@ -777,7 +777,7 @@
         <v>-0.1313131313131313</v>
       </c>
       <c r="B45" t="n">
-        <v>-3.165701113263619e-07</v>
+        <v>-3.385479624381818e-07</v>
       </c>
     </row>
     <row r="46">
@@ -785,7 +785,7 @@
         <v>-0.111111111111111</v>
       </c>
       <c r="B46" t="n">
-        <v>-2.876468741309711e-07</v>
+        <v>-3.677540730084058e-07</v>
       </c>
     </row>
     <row r="47">
@@ -793,7 +793,7 @@
         <v>-0.09090909090909083</v>
       </c>
       <c r="B47" t="n">
-        <v>-2.515582922515326e-07</v>
+        <v>-3.889683696086966e-07</v>
       </c>
     </row>
     <row r="48">
@@ -801,7 +801,7 @@
         <v>-0.07070707070707061</v>
       </c>
       <c r="B48" t="n">
-        <v>-2.987090651912121e-07</v>
+        <v>-3.225603881770982e-07</v>
       </c>
     </row>
     <row r="49">
@@ -809,7 +809,7 @@
         <v>-0.05050505050505039</v>
       </c>
       <c r="B49" t="n">
-        <v>-2.250923594159885e-07</v>
+        <v>-1.648225720927946e-07</v>
       </c>
     </row>
     <row r="50">
@@ -817,7 +817,7 @@
         <v>-0.03030303030303028</v>
       </c>
       <c r="B50" t="n">
-        <v>-2.306114494350772e-07</v>
+        <v>-9.324375599342551e-08</v>
       </c>
     </row>
     <row r="51">
@@ -825,7 +825,7 @@
         <v>-0.01010101010101006</v>
       </c>
       <c r="B51" t="n">
-        <v>-4.40269528224814e-08</v>
+        <v>-5.847842163067593e-08</v>
       </c>
     </row>
     <row r="52">
@@ -833,7 +833,7 @@
         <v>0.01010101010101017</v>
       </c>
       <c r="B52" t="n">
-        <v>1.723729819097495e-07</v>
+        <v>4.488131140356667e-09</v>
       </c>
     </row>
     <row r="53">
@@ -841,7 +841,7 @@
         <v>0.0303030303030305</v>
       </c>
       <c r="B53" t="n">
-        <v>2.007766277133314e-07</v>
+        <v>9.09376307571961e-08</v>
       </c>
     </row>
     <row r="54">
@@ -849,7 +849,7 @@
         <v>0.05050505050505061</v>
       </c>
       <c r="B54" t="n">
-        <v>3.712907658020875e-07</v>
+        <v>3.929256764762067e-07</v>
       </c>
     </row>
     <row r="55">
@@ -857,7 +857,7 @@
         <v>0.07070707070707072</v>
       </c>
       <c r="B55" t="n">
-        <v>4.541705470414664e-07</v>
+        <v>5.29171431511419e-07</v>
       </c>
     </row>
     <row r="56">
@@ -865,7 +865,7 @@
         <v>0.09090909090909105</v>
       </c>
       <c r="B56" t="n">
-        <v>6.726511621544484e-07</v>
+        <v>7.538189408858968e-07</v>
       </c>
     </row>
     <row r="57">
@@ -873,7 +873,7 @@
         <v>0.1111111111111112</v>
       </c>
       <c r="B57" t="n">
-        <v>1.036482125662863e-06</v>
+        <v>1.04165915846708e-06</v>
       </c>
     </row>
     <row r="58">
@@ -881,7 +881,7 @@
         <v>0.1313131313131315</v>
       </c>
       <c r="B58" t="n">
-        <v>1.349360266580986e-06</v>
+        <v>1.335770100317374e-06</v>
       </c>
     </row>
     <row r="59">
@@ -889,7 +889,7 @@
         <v>0.1515151515151516</v>
       </c>
       <c r="B59" t="n">
-        <v>1.832143582444237e-06</v>
+        <v>1.742218431745781e-06</v>
       </c>
     </row>
     <row r="60">
@@ -897,7 +897,7 @@
         <v>0.1717171717171717</v>
       </c>
       <c r="B60" t="n">
-        <v>2.242665969315958e-06</v>
+        <v>2.294154627726243e-06</v>
       </c>
     </row>
     <row r="61">
@@ -905,7 +905,7 @@
         <v>0.191919191919192</v>
       </c>
       <c r="B61" t="n">
-        <v>2.902618037826901e-06</v>
+        <v>2.917582292934823e-06</v>
       </c>
     </row>
     <row r="62">
@@ -913,7 +913,7 @@
         <v>0.2121212121212122</v>
       </c>
       <c r="B62" t="n">
-        <v>3.666497225606559e-06</v>
+        <v>3.670516210731948e-06</v>
       </c>
     </row>
     <row r="63">
@@ -921,7 +921,7 @@
         <v>0.2323232323232325</v>
       </c>
       <c r="B63" t="n">
-        <v>4.59487443072613e-06</v>
+        <v>4.656219299382259e-06</v>
       </c>
     </row>
     <row r="64">
@@ -929,7 +929,7 @@
         <v>0.2525252525252526</v>
       </c>
       <c r="B64" t="n">
-        <v>5.806808769155984e-06</v>
+        <v>5.779220638904293e-06</v>
       </c>
     </row>
     <row r="65">
@@ -937,7 +937,7 @@
         <v>0.2727272727272729</v>
       </c>
       <c r="B65" t="n">
-        <v>7.199015087983707e-06</v>
+        <v>7.162735333140222e-06</v>
       </c>
     </row>
     <row r="66">
@@ -945,7 +945,7 @@
         <v>0.292929292929293</v>
       </c>
       <c r="B66" t="n">
-        <v>8.760538850001666e-06</v>
+        <v>8.813805130121156e-06</v>
       </c>
     </row>
     <row r="67">
@@ -953,7 +953,7 @@
         <v>0.3131313131313131</v>
       </c>
       <c r="B67" t="n">
-        <v>1.095981195897291e-05</v>
+        <v>1.092478947037261e-05</v>
       </c>
     </row>
     <row r="68">
@@ -961,7 +961,7 @@
         <v>0.3333333333333335</v>
       </c>
       <c r="B68" t="n">
-        <v>1.358437774505031e-05</v>
+        <v>1.345933666941183e-05</v>
       </c>
     </row>
     <row r="69">
@@ -969,7 +969,7 @@
         <v>0.3535353535353536</v>
       </c>
       <c r="B69" t="n">
-        <v>1.663658827430071e-05</v>
+        <v>1.663453221325418e-05</v>
       </c>
     </row>
     <row r="70">
@@ -977,7 +977,7 @@
         <v>0.3737373737373739</v>
       </c>
       <c r="B70" t="n">
-        <v>2.050239533213828e-05</v>
+        <v>2.051958018115764e-05</v>
       </c>
     </row>
     <row r="71">
@@ -985,7 +985,7 @@
         <v>0.393939393939394</v>
       </c>
       <c r="B71" t="n">
-        <v>2.518469289311147e-05</v>
+        <v>2.521834361017301e-05</v>
       </c>
     </row>
     <row r="72">
@@ -993,7 +993,7 @@
         <v>0.4141414141414144</v>
       </c>
       <c r="B72" t="n">
-        <v>3.089133031641453e-05</v>
+        <v>3.095931756898266e-05</v>
       </c>
     </row>
     <row r="73">
@@ -1001,7 +1001,7 @@
         <v>0.4343434343434345</v>
       </c>
       <c r="B73" t="n">
-        <v>3.795946586244562e-05</v>
+        <v>3.797890499325039e-05</v>
       </c>
     </row>
     <row r="74">
@@ -1009,7 +1009,7 @@
         <v>0.4545454545454546</v>
       </c>
       <c r="B74" t="n">
-        <v>4.656734893733359e-05</v>
+        <v>4.662654674521361e-05</v>
       </c>
     </row>
     <row r="75">
@@ -1017,7 +1017,7 @@
         <v>0.4747474747474749</v>
       </c>
       <c r="B75" t="n">
-        <v>5.718896302251697e-05</v>
+        <v>5.719093718878788e-05</v>
       </c>
     </row>
     <row r="76">
@@ -1025,7 +1025,7 @@
         <v>0.494949494949495</v>
       </c>
       <c r="B76" t="n">
-        <v>6.998247813689067e-05</v>
+        <v>7.002985281018016e-05</v>
       </c>
     </row>
     <row r="77">
@@ -1033,7 +1033,7 @@
         <v>0.5151515151515154</v>
       </c>
       <c r="B77" t="n">
-        <v>8.581424662052897e-05</v>
+        <v>8.576550582179591e-05</v>
       </c>
     </row>
     <row r="78">
@@ -1041,7 +1041,7 @@
         <v>0.5353535353535355</v>
       </c>
       <c r="B78" t="n">
-        <v>0.0001051868960436889</v>
+        <v>0.0001052457975369309</v>
       </c>
     </row>
     <row r="79">
@@ -1049,7 +1049,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="B79" t="n">
-        <v>0.0001288815386883742</v>
+        <v>0.0001289352247756017</v>
       </c>
     </row>
     <row r="80">
@@ -1057,7 +1057,7 @@
         <v>0.5757575757575759</v>
       </c>
       <c r="B80" t="n">
-        <v>0.0001578102338567534</v>
+        <v>0.0001577669015485762</v>
       </c>
     </row>
     <row r="81">
@@ -1065,7 +1065,7 @@
         <v>0.595959595959596</v>
       </c>
       <c r="B81" t="n">
-        <v>0.000193267118001684</v>
+        <v>0.0001931855206371411</v>
       </c>
     </row>
     <row r="82">
@@ -1073,7 +1073,7 @@
         <v>0.6161616161616164</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0002366354389069478</v>
+        <v>0.0002366290977800479</v>
       </c>
     </row>
     <row r="83">
@@ -1081,7 +1081,7 @@
         <v>0.6363636363636365</v>
       </c>
       <c r="B83" t="n">
-        <v>0.0002896366667663872</v>
+        <v>0.0002896805735329998</v>
       </c>
     </row>
     <row r="84">
@@ -1089,7 +1089,7 @@
         <v>0.6565656565656568</v>
       </c>
       <c r="B84" t="n">
-        <v>0.000354696616395284</v>
+        <v>0.000354620992086229</v>
       </c>
     </row>
     <row r="85">
@@ -1097,7 +1097,7 @@
         <v>0.6767676767676769</v>
       </c>
       <c r="B85" t="n">
-        <v>0.0004341139463977687</v>
+        <v>0.0004340841647071061</v>
       </c>
     </row>
     <row r="86">
@@ -1105,7 +1105,7 @@
         <v>0.696969696969697</v>
       </c>
       <c r="B86" t="n">
-        <v>0.0005314261747693485</v>
+        <v>0.0005314996849678932</v>
       </c>
     </row>
     <row r="87">
@@ -1113,7 +1113,7 @@
         <v>0.7171717171717173</v>
       </c>
       <c r="B87" t="n">
-        <v>0.0006505067244635547</v>
+        <v>0.0006504832084749676</v>
       </c>
     </row>
     <row r="88">
@@ -1121,7 +1121,7 @@
         <v>0.7373737373737375</v>
       </c>
       <c r="B88" t="n">
-        <v>0.0007963490827830135</v>
+        <v>0.0007962254630512937</v>
       </c>
     </row>
     <row r="89">
@@ -1129,7 +1129,7 @@
         <v>0.7575757575757578</v>
       </c>
       <c r="B89" t="n">
-        <v>0.0009745897585617104</v>
+        <v>0.0009746884037445674</v>
       </c>
     </row>
     <row r="90">
@@ -1137,7 +1137,7 @@
         <v>0.7777777777777779</v>
       </c>
       <c r="B90" t="n">
-        <v>0.001193026281591776</v>
+        <v>0.0011929930476819</v>
       </c>
     </row>
     <row r="91">
@@ -1145,7 +1145,7 @@
         <v>0.7979797979797982</v>
       </c>
       <c r="B91" t="n">
-        <v>0.001460261193891527</v>
+        <v>0.001460275308506377</v>
       </c>
     </row>
     <row r="92">
@@ -1153,7 +1153,7 @@
         <v>0.8181818181818183</v>
       </c>
       <c r="B92" t="n">
-        <v>0.001787251734692133</v>
+        <v>0.001787261370012793</v>
       </c>
     </row>
     <row r="93">
@@ -1161,7 +1161,7 @@
         <v>0.8383838383838385</v>
       </c>
       <c r="B93" t="n">
-        <v>0.002187410475714632</v>
+        <v>0.002187452013428648</v>
       </c>
     </row>
     <row r="94">
@@ -1169,7 +1169,7 @@
         <v>0.8585858585858588</v>
       </c>
       <c r="B94" t="n">
-        <v>0.002677311629068006</v>
+        <v>0.002677150586913445</v>
       </c>
     </row>
     <row r="95">
@@ -1177,7 +1177,7 @@
         <v>0.8787878787878789</v>
       </c>
       <c r="B95" t="n">
-        <v>0.003276679445598621</v>
+        <v>0.003276652528647134</v>
       </c>
     </row>
     <row r="96">
@@ -1185,7 +1185,7 @@
         <v>0.8989898989898992</v>
       </c>
       <c r="B96" t="n">
-        <v>0.004010343182527256</v>
+        <v>0.004010332390760075</v>
       </c>
     </row>
     <row r="97">
@@ -1193,7 +1193,7 @@
         <v>0.9191919191919193</v>
       </c>
       <c r="B97" t="n">
-        <v>0.004908193780996948</v>
+        <v>0.004908266829048363</v>
       </c>
     </row>
     <row r="98">
@@ -1201,7 +1201,7 @@
         <v>0.9393939393939394</v>
       </c>
       <c r="B98" t="n">
-        <v>0.006007073588021805</v>
+        <v>0.006007149278173167</v>
       </c>
     </row>
     <row r="99">
@@ -1209,7 +1209,7 @@
         <v>0.9595959595959598</v>
       </c>
       <c r="B99" t="n">
-        <v>0.007352051387184968</v>
+        <v>0.007352179730496839</v>
       </c>
     </row>
     <row r="100">
@@ -1217,7 +1217,7 @@
         <v>0.9797979797979799</v>
       </c>
       <c r="B100" t="n">
-        <v>0.00899815085298198</v>
+        <v>0.008998122974222329</v>
       </c>
     </row>
     <row r="101">
@@ -1225,7 +1225,7 @@
         <v>1</v>
       </c>
       <c r="B101" t="n">
-        <v>0.01101268429071972</v>
+        <v>0.01101274539731444</v>
       </c>
     </row>
   </sheetData>

--- a/datos/valido_uA_mV.xlsx
+++ b/datos/valido_uA_mV.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="datos_IV" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,7 +425,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>V secundario (mV)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>I (uA)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>I secundario (uA)</t>
         </is>
       </c>
     </row>
@@ -433,7 +444,13 @@
         <v>-1</v>
       </c>
       <c r="B2" t="n">
-        <v>-5.176492041818887e-07</v>
+        <v>-1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-5.575296889108543e-07</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-5.575296889108543e-07</v>
       </c>
     </row>
     <row r="3">
@@ -441,7 +458,13 @@
         <v>-0.9797979797979798</v>
       </c>
       <c r="B3" t="n">
-        <v>-4.389874124475519e-07</v>
+        <v>-0.9797979797979798</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-5.148440809016539e-07</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-5.148440809016539e-07</v>
       </c>
     </row>
     <row r="4">
@@ -449,7 +472,13 @@
         <v>-0.9595959595959596</v>
       </c>
       <c r="B4" t="n">
-        <v>-5.647252093437225e-07</v>
+        <v>-0.9595959595959596</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-5.347462706556628e-07</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-5.347462706556628e-07</v>
       </c>
     </row>
     <row r="5">
@@ -457,7 +486,13 @@
         <v>-0.9393939393939394</v>
       </c>
       <c r="B5" t="n">
-        <v>-5.85299352012887e-07</v>
+        <v>-0.9393939393939394</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-5.847113929404075e-07</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-5.847113929404075e-07</v>
       </c>
     </row>
     <row r="6">
@@ -465,7 +500,13 @@
         <v>-0.9191919191919192</v>
       </c>
       <c r="B6" t="n">
-        <v>-5.809535670103779e-07</v>
+        <v>-0.9191919191919192</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-5.667232667282795e-07</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-5.667232667282795e-07</v>
       </c>
     </row>
     <row r="7">
@@ -473,7 +514,13 @@
         <v>-0.898989898989899</v>
       </c>
       <c r="B7" t="n">
-        <v>-5.156891664575949e-07</v>
+        <v>-0.898989898989899</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-4.676040724001424e-07</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-4.676040724001424e-07</v>
       </c>
     </row>
     <row r="8">
@@ -481,7 +528,13 @@
         <v>-0.8787878787878788</v>
       </c>
       <c r="B8" t="n">
-        <v>-4.490279172474666e-07</v>
+        <v>-0.8787878787878788</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-5.119355935894203e-07</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-5.119355935894203e-07</v>
       </c>
     </row>
     <row r="9">
@@ -489,7 +542,13 @@
         <v>-0.8585858585858586</v>
       </c>
       <c r="B9" t="n">
-        <v>-4.706890576087513e-07</v>
+        <v>-0.8585858585858586</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-5.264578543262929e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-5.264578543262929e-07</v>
       </c>
     </row>
     <row r="10">
@@ -497,7 +556,13 @@
         <v>-0.8383838383838383</v>
       </c>
       <c r="B10" t="n">
-        <v>-4.479213625227671e-07</v>
+        <v>-0.8383838383838383</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-4.953883344956148e-07</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-4.953883344956148e-07</v>
       </c>
     </row>
     <row r="11">
@@ -505,7 +570,13 @@
         <v>-0.8181818181818181</v>
       </c>
       <c r="B11" t="n">
-        <v>-4.618398690318095e-07</v>
+        <v>-0.8181818181818181</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-4.092045900681612e-07</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-4.092045900681612e-07</v>
       </c>
     </row>
     <row r="12">
@@ -513,7 +584,13 @@
         <v>-0.797979797979798</v>
       </c>
       <c r="B12" t="n">
-        <v>-5.089402919892034e-07</v>
+        <v>-0.797979797979798</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-4.209827749762889e-07</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-4.209827749762889e-07</v>
       </c>
     </row>
     <row r="13">
@@ -521,7 +598,13 @@
         <v>-0.7777777777777778</v>
       </c>
       <c r="B13" t="n">
-        <v>-5.014288326622062e-07</v>
+        <v>-0.7777777777777778</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-4.612858670195686e-07</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-4.612858670195686e-07</v>
       </c>
     </row>
     <row r="14">
@@ -529,7 +612,13 @@
         <v>-0.7575757575757576</v>
       </c>
       <c r="B14" t="n">
-        <v>-4.679261174936258e-07</v>
+        <v>-0.7575757575757576</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-5.065445859905182e-07</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-5.065445859905182e-07</v>
       </c>
     </row>
     <row r="15">
@@ -537,7 +626,13 @@
         <v>-0.7373737373737373</v>
       </c>
       <c r="B15" t="n">
-        <v>-4.42349849801832e-07</v>
+        <v>-0.7373737373737373</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-3.520954293841247e-07</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-3.520954293841247e-07</v>
       </c>
     </row>
     <row r="16">
@@ -545,7 +640,13 @@
         <v>-0.7171717171717171</v>
       </c>
       <c r="B16" t="n">
-        <v>-5.283606394601131e-07</v>
+        <v>-0.7171717171717171</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-4.92136604513268e-07</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-4.92136604513268e-07</v>
       </c>
     </row>
     <row r="17">
@@ -553,7 +654,13 @@
         <v>-0.696969696969697</v>
       </c>
       <c r="B17" t="n">
-        <v>-5.181032263927268e-07</v>
+        <v>-0.696969696969697</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-5.543614761365328e-07</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-5.543614761365328e-07</v>
       </c>
     </row>
     <row r="18">
@@ -561,7 +668,13 @@
         <v>-0.6767676767676767</v>
       </c>
       <c r="B18" t="n">
-        <v>-4.868728400727183e-07</v>
+        <v>-0.6767676767676767</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-4.519523198431427e-07</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-4.519523198431427e-07</v>
       </c>
     </row>
     <row r="19">
@@ -569,7 +682,13 @@
         <v>-0.6565656565656566</v>
       </c>
       <c r="B19" t="n">
-        <v>-6.024467961350137e-07</v>
+        <v>-0.6565656565656566</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-5.16190717736609e-07</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-5.16190717736609e-07</v>
       </c>
     </row>
     <row r="20">
@@ -577,7 +696,13 @@
         <v>-0.6363636363636364</v>
       </c>
       <c r="B20" t="n">
-        <v>-4.654944744157926e-07</v>
+        <v>-0.6363636363636364</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-5.004048458439175e-07</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-5.004048458439175e-07</v>
       </c>
     </row>
     <row r="21">
@@ -585,7 +710,13 @@
         <v>-0.6161616161616161</v>
       </c>
       <c r="B21" t="n">
-        <v>-4.589624648089605e-07</v>
+        <v>-0.6161616161616161</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-4.957121174452567e-07</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-4.957121174452567e-07</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +724,13 @@
         <v>-0.5959595959595959</v>
       </c>
       <c r="B22" t="n">
-        <v>-4.643786253700058e-07</v>
+        <v>-0.5959595959595959</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-4.426299203015761e-07</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-4.426299203015761e-07</v>
       </c>
     </row>
     <row r="23">
@@ -601,7 +738,13 @@
         <v>-0.5757575757575757</v>
       </c>
       <c r="B23" t="n">
-        <v>-4.564197452386764e-07</v>
+        <v>-0.5757575757575757</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-4.549314539055884e-07</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-4.549314539055884e-07</v>
       </c>
     </row>
     <row r="24">
@@ -609,7 +752,13 @@
         <v>-0.5555555555555556</v>
       </c>
       <c r="B24" t="n">
-        <v>-5.419908513893661e-07</v>
+        <v>-0.5555555555555556</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-4.193315490114515e-07</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-4.193315490114515e-07</v>
       </c>
     </row>
     <row r="25">
@@ -617,7 +766,13 @@
         <v>-0.5353535353535352</v>
       </c>
       <c r="B25" t="n">
-        <v>-4.977315549626457e-07</v>
+        <v>-0.5353535353535352</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-4.806814691873522e-07</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-4.806814691873522e-07</v>
       </c>
     </row>
     <row r="26">
@@ -625,7 +780,13 @@
         <v>-0.5151515151515151</v>
       </c>
       <c r="B26" t="n">
-        <v>-4.673231876594135e-07</v>
+        <v>-0.5151515151515151</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-5.218603766575411e-07</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-5.218603766575411e-07</v>
       </c>
     </row>
     <row r="27">
@@ -633,7 +794,13 @@
         <v>-0.4949494949494949</v>
       </c>
       <c r="B27" t="n">
-        <v>-4.560147793322681e-07</v>
+        <v>-0.4949494949494949</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-4.913541524508792e-07</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-4.913541524508792e-07</v>
       </c>
     </row>
     <row r="28">
@@ -641,7 +808,13 @@
         <v>-0.4747474747474747</v>
       </c>
       <c r="B28" t="n">
-        <v>-4.943562074595324e-07</v>
+        <v>-0.4747474747474747</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-4.370079480493374e-07</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-4.370079480493374e-07</v>
       </c>
     </row>
     <row r="29">
@@ -649,7 +822,13 @@
         <v>-0.4545454545454545</v>
       </c>
       <c r="B29" t="n">
-        <v>-5.555109746110451e-07</v>
+        <v>-0.4545454545454545</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-4.055195496470887e-07</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-4.055195496470887e-07</v>
       </c>
     </row>
     <row r="30">
@@ -657,7 +836,13 @@
         <v>-0.4343434343434343</v>
       </c>
       <c r="B30" t="n">
-        <v>-5.280703802390346e-07</v>
+        <v>-0.4343434343434343</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-4.825962986926074e-07</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-4.825962986926074e-07</v>
       </c>
     </row>
     <row r="31">
@@ -665,7 +850,13 @@
         <v>-0.4141414141414141</v>
       </c>
       <c r="B31" t="n">
-        <v>-4.756273001273253e-07</v>
+        <v>-0.4141414141414141</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-4.280701871081991e-07</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-4.280701871081991e-07</v>
       </c>
     </row>
     <row r="32">
@@ -673,7 +864,13 @@
         <v>-0.3939393939393939</v>
       </c>
       <c r="B32" t="n">
-        <v>-5.194424025494453e-07</v>
+        <v>-0.3939393939393939</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-4.016715413802428e-07</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-4.016715413802428e-07</v>
       </c>
     </row>
     <row r="33">
@@ -681,7 +878,13 @@
         <v>-0.3737373737373737</v>
       </c>
       <c r="B33" t="n">
-        <v>-4.767034262816237e-07</v>
+        <v>-0.3737373737373737</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-5.006037076176914e-07</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-5.006037076176914e-07</v>
       </c>
     </row>
     <row r="34">
@@ -689,7 +892,13 @@
         <v>-0.3535353535353535</v>
       </c>
       <c r="B34" t="n">
-        <v>-4.622545389507718e-07</v>
+        <v>-0.3535353535353535</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-4.602387801259682e-07</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-4.602387801259682e-07</v>
       </c>
     </row>
     <row r="35">
@@ -697,7 +906,13 @@
         <v>-0.3333333333333333</v>
       </c>
       <c r="B35" t="n">
-        <v>-4.836521320695332e-07</v>
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-5.802316168235663e-07</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-5.802316168235663e-07</v>
       </c>
     </row>
     <row r="36">
@@ -705,7 +920,13 @@
         <v>-0.313131313131313</v>
       </c>
       <c r="B36" t="n">
-        <v>-5.529235736238256e-07</v>
+        <v>-0.313131313131313</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-4.651579722695093e-07</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-4.651579722695093e-07</v>
       </c>
     </row>
     <row r="37">
@@ -713,7 +934,13 @@
         <v>-0.2929292929292928</v>
       </c>
       <c r="B37" t="n">
-        <v>-4.73194569236108e-07</v>
+        <v>-0.2929292929292928</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-4.642099082826803e-07</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-4.642099082826803e-07</v>
       </c>
     </row>
     <row r="38">
@@ -721,7 +948,13 @@
         <v>-0.2727272727272727</v>
       </c>
       <c r="B38" t="n">
-        <v>-4.506339267283381e-07</v>
+        <v>-0.2727272727272727</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-3.337707254393349e-07</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-3.337707254393349e-07</v>
       </c>
     </row>
     <row r="39">
@@ -729,7 +962,13 @@
         <v>-0.2525252525252525</v>
       </c>
       <c r="B39" t="n">
-        <v>-5.901894209931789e-07</v>
+        <v>-0.2525252525252525</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-4.651439293879137e-07</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-4.651439293879137e-07</v>
       </c>
     </row>
     <row r="40">
@@ -737,7 +976,13 @@
         <v>-0.2323232323232323</v>
       </c>
       <c r="B40" t="n">
-        <v>-4.911611832080171e-07</v>
+        <v>-0.2323232323232323</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-4.451030050634719e-07</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-4.451030050634719e-07</v>
       </c>
     </row>
     <row r="41">
@@ -745,7 +990,13 @@
         <v>-0.212121212121212</v>
       </c>
       <c r="B41" t="n">
-        <v>-4.865140525470511e-07</v>
+        <v>-0.212121212121212</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-4.185127255031851e-07</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-4.185127255031851e-07</v>
       </c>
     </row>
     <row r="42">
@@ -753,7 +1004,13 @@
         <v>-0.1919191919191918</v>
       </c>
       <c r="B42" t="n">
-        <v>-4.71291067338697e-07</v>
+        <v>-0.1919191919191918</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-4.84886151248074e-07</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-4.84886151248074e-07</v>
       </c>
     </row>
     <row r="43">
@@ -761,7 +1018,13 @@
         <v>-0.1717171717171716</v>
       </c>
       <c r="B43" t="n">
-        <v>-3.786554226942276e-07</v>
+        <v>-0.1717171717171716</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-3.895212636195041e-07</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-3.895212636195041e-07</v>
       </c>
     </row>
     <row r="44">
@@ -769,7 +1032,13 @@
         <v>-0.1515151515151515</v>
       </c>
       <c r="B44" t="n">
-        <v>-3.359830326826454e-07</v>
+        <v>-0.1515151515151515</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-3.595148749172971e-07</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-3.595148749172971e-07</v>
       </c>
     </row>
     <row r="45">
@@ -777,7 +1046,13 @@
         <v>-0.1313131313131313</v>
       </c>
       <c r="B45" t="n">
-        <v>-3.385479624381818e-07</v>
+        <v>-0.1313131313131313</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-3.067539368494962e-07</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-3.067539368494962e-07</v>
       </c>
     </row>
     <row r="46">
@@ -785,7 +1060,13 @@
         <v>-0.111111111111111</v>
       </c>
       <c r="B46" t="n">
-        <v>-3.677540730084058e-07</v>
+        <v>-0.111111111111111</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-3.603614109140464e-07</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-3.603614109140464e-07</v>
       </c>
     </row>
     <row r="47">
@@ -793,7 +1074,13 @@
         <v>-0.09090909090909083</v>
       </c>
       <c r="B47" t="n">
-        <v>-3.889683696086966e-07</v>
+        <v>-0.09090909090909083</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-3.093142146378406e-07</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-3.093142146378406e-07</v>
       </c>
     </row>
     <row r="48">
@@ -801,7 +1088,13 @@
         <v>-0.07070707070707061</v>
       </c>
       <c r="B48" t="n">
-        <v>-3.225603881770982e-07</v>
+        <v>-0.07070707070707061</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-2.147085909935012e-07</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-2.147085909935012e-07</v>
       </c>
     </row>
     <row r="49">
@@ -809,7 +1102,13 @@
         <v>-0.05050505050505039</v>
       </c>
       <c r="B49" t="n">
-        <v>-1.648225720927946e-07</v>
+        <v>-0.05050505050505039</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-2.675654084387547e-07</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-2.675654084387547e-07</v>
       </c>
     </row>
     <row r="50">
@@ -817,7 +1116,13 @@
         <v>-0.03030303030303028</v>
       </c>
       <c r="B50" t="n">
-        <v>-9.324375599342551e-08</v>
+        <v>-0.03030303030303028</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-1.062234497794954e-07</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-1.062234497794954e-07</v>
       </c>
     </row>
     <row r="51">
@@ -825,7 +1130,13 @@
         <v>-0.01010101010101006</v>
       </c>
       <c r="B51" t="n">
-        <v>-5.847842163067593e-08</v>
+        <v>-0.01010101010101006</v>
+      </c>
+      <c r="C51" t="n">
+        <v>4.842669808489338e-09</v>
+      </c>
+      <c r="D51" t="n">
+        <v>4.842669808489338e-09</v>
       </c>
     </row>
     <row r="52">
@@ -833,7 +1144,13 @@
         <v>0.01010101010101017</v>
       </c>
       <c r="B52" t="n">
-        <v>4.488131140356667e-09</v>
+        <v>0.01010101010101017</v>
+      </c>
+      <c r="C52" t="n">
+        <v>9.576646182324681e-08</v>
+      </c>
+      <c r="D52" t="n">
+        <v>9.576646182324681e-08</v>
       </c>
     </row>
     <row r="53">
@@ -841,7 +1158,13 @@
         <v>0.0303030303030305</v>
       </c>
       <c r="B53" t="n">
-        <v>9.09376307571961e-08</v>
+        <v>0.0303030303030305</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1.7109702380072e-07</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.7109702380072e-07</v>
       </c>
     </row>
     <row r="54">
@@ -849,7 +1172,13 @@
         <v>0.05050505050505061</v>
       </c>
       <c r="B54" t="n">
-        <v>3.929256764762067e-07</v>
+        <v>0.05050505050505061</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3.098915085153472e-07</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3.098915085153472e-07</v>
       </c>
     </row>
     <row r="55">
@@ -857,7 +1186,13 @@
         <v>0.07070707070707072</v>
       </c>
       <c r="B55" t="n">
-        <v>5.29171431511419e-07</v>
+        <v>0.07070707070707072</v>
+      </c>
+      <c r="C55" t="n">
+        <v>4.901713655412426e-07</v>
+      </c>
+      <c r="D55" t="n">
+        <v>4.901713655412426e-07</v>
       </c>
     </row>
     <row r="56">
@@ -865,7 +1200,13 @@
         <v>0.09090909090909105</v>
       </c>
       <c r="B56" t="n">
-        <v>7.538189408858968e-07</v>
+        <v>0.09090909090909105</v>
+      </c>
+      <c r="C56" t="n">
+        <v>7.745687192969508e-07</v>
+      </c>
+      <c r="D56" t="n">
+        <v>7.745687192969508e-07</v>
       </c>
     </row>
     <row r="57">
@@ -873,7 +1214,13 @@
         <v>0.1111111111111112</v>
       </c>
       <c r="B57" t="n">
-        <v>1.04165915846708e-06</v>
+        <v>0.1111111111111112</v>
+      </c>
+      <c r="C57" t="n">
+        <v>9.872895306961562e-07</v>
+      </c>
+      <c r="D57" t="n">
+        <v>9.872895306961562e-07</v>
       </c>
     </row>
     <row r="58">
@@ -881,7 +1228,13 @@
         <v>0.1313131313131315</v>
       </c>
       <c r="B58" t="n">
-        <v>1.335770100317374e-06</v>
+        <v>0.1313131313131315</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1.327645275697644e-06</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.327645275697644e-06</v>
       </c>
     </row>
     <row r="59">
@@ -889,7 +1242,13 @@
         <v>0.1515151515151516</v>
       </c>
       <c r="B59" t="n">
-        <v>1.742218431745781e-06</v>
+        <v>0.1515151515151516</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1.694723859625552e-06</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.694723859625552e-06</v>
       </c>
     </row>
     <row r="60">
@@ -897,7 +1256,13 @@
         <v>0.1717171717171717</v>
       </c>
       <c r="B60" t="n">
-        <v>2.294154627726243e-06</v>
+        <v>0.1717171717171717</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2.294447871360126e-06</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2.294447871360126e-06</v>
       </c>
     </row>
     <row r="61">
@@ -905,7 +1270,13 @@
         <v>0.191919191919192</v>
       </c>
       <c r="B61" t="n">
-        <v>2.917582292934823e-06</v>
+        <v>0.191919191919192</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2.917185704004294e-06</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2.917185704004294e-06</v>
       </c>
     </row>
     <row r="62">
@@ -913,7 +1284,13 @@
         <v>0.2121212121212122</v>
       </c>
       <c r="B62" t="n">
-        <v>3.670516210731948e-06</v>
+        <v>0.2121212121212122</v>
+      </c>
+      <c r="C62" t="n">
+        <v>3.775554366195127e-06</v>
+      </c>
+      <c r="D62" t="n">
+        <v>3.775554366195127e-06</v>
       </c>
     </row>
     <row r="63">
@@ -921,7 +1298,13 @@
         <v>0.2323232323232325</v>
       </c>
       <c r="B63" t="n">
-        <v>4.656219299382259e-06</v>
+        <v>0.2323232323232325</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4.62283127083775e-06</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4.62283127083775e-06</v>
       </c>
     </row>
     <row r="64">
@@ -929,7 +1312,13 @@
         <v>0.2525252525252526</v>
       </c>
       <c r="B64" t="n">
-        <v>5.779220638904293e-06</v>
+        <v>0.2525252525252526</v>
+      </c>
+      <c r="C64" t="n">
+        <v>5.716053542055635e-06</v>
+      </c>
+      <c r="D64" t="n">
+        <v>5.716053542055635e-06</v>
       </c>
     </row>
     <row r="65">
@@ -937,7 +1326,13 @@
         <v>0.2727272727272729</v>
       </c>
       <c r="B65" t="n">
-        <v>7.162735333140222e-06</v>
+        <v>0.2727272727272729</v>
+      </c>
+      <c r="C65" t="n">
+        <v>7.130983257843301e-06</v>
+      </c>
+      <c r="D65" t="n">
+        <v>7.130983257843301e-06</v>
       </c>
     </row>
     <row r="66">
@@ -945,7 +1340,13 @@
         <v>0.292929292929293</v>
       </c>
       <c r="B66" t="n">
-        <v>8.813805130121156e-06</v>
+        <v>0.292929292929293</v>
+      </c>
+      <c r="C66" t="n">
+        <v>8.865497587017131e-06</v>
+      </c>
+      <c r="D66" t="n">
+        <v>8.865497587017131e-06</v>
       </c>
     </row>
     <row r="67">
@@ -953,7 +1354,13 @@
         <v>0.3131313131313131</v>
       </c>
       <c r="B67" t="n">
-        <v>1.092478947037261e-05</v>
+        <v>0.3131313131313131</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1.092536336147938e-05</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.092536336147938e-05</v>
       </c>
     </row>
     <row r="68">
@@ -961,7 +1368,13 @@
         <v>0.3333333333333335</v>
       </c>
       <c r="B68" t="n">
-        <v>1.345933666941183e-05</v>
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1.35191485806199e-05</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.35191485806199e-05</v>
       </c>
     </row>
     <row r="69">
@@ -969,7 +1382,13 @@
         <v>0.3535353535353536</v>
       </c>
       <c r="B69" t="n">
-        <v>1.663453221325418e-05</v>
+        <v>0.3535353535353536</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1.664117770441317e-05</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.664117770441317e-05</v>
       </c>
     </row>
     <row r="70">
@@ -977,7 +1396,13 @@
         <v>0.3737373737373739</v>
       </c>
       <c r="B70" t="n">
-        <v>2.051958018115764e-05</v>
+        <v>0.3737373737373739</v>
+      </c>
+      <c r="C70" t="n">
+        <v>2.050257051613216e-05</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2.050257051613216e-05</v>
       </c>
     </row>
     <row r="71">
@@ -985,7 +1410,13 @@
         <v>0.393939393939394</v>
       </c>
       <c r="B71" t="n">
-        <v>2.521834361017301e-05</v>
+        <v>0.393939393939394</v>
+      </c>
+      <c r="C71" t="n">
+        <v>2.522507614008946e-05</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2.522507614008946e-05</v>
       </c>
     </row>
     <row r="72">
@@ -993,7 +1424,13 @@
         <v>0.4141414141414144</v>
       </c>
       <c r="B72" t="n">
-        <v>3.095931756898266e-05</v>
+        <v>0.4141414141414144</v>
+      </c>
+      <c r="C72" t="n">
+        <v>3.094803655265468e-05</v>
+      </c>
+      <c r="D72" t="n">
+        <v>3.094803655265468e-05</v>
       </c>
     </row>
     <row r="73">
@@ -1001,7 +1438,13 @@
         <v>0.4343434343434345</v>
       </c>
       <c r="B73" t="n">
-        <v>3.797890499325039e-05</v>
+        <v>0.4343434343434345</v>
+      </c>
+      <c r="C73" t="n">
+        <v>3.801779997054857e-05</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3.801779997054857e-05</v>
       </c>
     </row>
     <row r="74">
@@ -1009,7 +1452,13 @@
         <v>0.4545454545454546</v>
       </c>
       <c r="B74" t="n">
-        <v>4.662654674521361e-05</v>
+        <v>0.4545454545454546</v>
+      </c>
+      <c r="C74" t="n">
+        <v>4.664479581293647e-05</v>
+      </c>
+      <c r="D74" t="n">
+        <v>4.664479581293647e-05</v>
       </c>
     </row>
     <row r="75">
@@ -1017,7 +1466,13 @@
         <v>0.4747474747474749</v>
       </c>
       <c r="B75" t="n">
-        <v>5.719093718878788e-05</v>
+        <v>0.4747474747474749</v>
+      </c>
+      <c r="C75" t="n">
+        <v>5.71396482007423e-05</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5.71396482007423e-05</v>
       </c>
     </row>
     <row r="76">
@@ -1025,7 +1480,13 @@
         <v>0.494949494949495</v>
       </c>
       <c r="B76" t="n">
-        <v>7.002985281018016e-05</v>
+        <v>0.494949494949495</v>
+      </c>
+      <c r="C76" t="n">
+        <v>6.997805281376935e-05</v>
+      </c>
+      <c r="D76" t="n">
+        <v>6.997805281376935e-05</v>
       </c>
     </row>
     <row r="77">
@@ -1033,7 +1494,13 @@
         <v>0.5151515151515154</v>
       </c>
       <c r="B77" t="n">
-        <v>8.576550582179591e-05</v>
+        <v>0.5151515151515154</v>
+      </c>
+      <c r="C77" t="n">
+        <v>8.592957548516481e-05</v>
+      </c>
+      <c r="D77" t="n">
+        <v>8.592957548516481e-05</v>
       </c>
     </row>
     <row r="78">
@@ -1041,7 +1508,13 @@
         <v>0.5353535353535355</v>
       </c>
       <c r="B78" t="n">
-        <v>0.0001052457975369309</v>
+        <v>0.5353535353535355</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.0001052061141983167</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.0001052061141983167</v>
       </c>
     </row>
     <row r="79">
@@ -1049,7 +1522,13 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="B79" t="n">
-        <v>0.0001289352247756017</v>
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.000128864425571345</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.000128864425571345</v>
       </c>
     </row>
     <row r="80">
@@ -1057,7 +1536,13 @@
         <v>0.5757575757575759</v>
       </c>
       <c r="B80" t="n">
-        <v>0.0001577669015485762</v>
+        <v>0.5757575757575759</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.0001577521967310831</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.0001577521967310831</v>
       </c>
     </row>
     <row r="81">
@@ -1065,7 +1550,13 @@
         <v>0.595959595959596</v>
       </c>
       <c r="B81" t="n">
-        <v>0.0001931855206371411</v>
+        <v>0.595959595959596</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.0001932009353466077</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.0001932009353466077</v>
       </c>
     </row>
     <row r="82">
@@ -1073,7 +1564,13 @@
         <v>0.6161616161616164</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0002366290977800479</v>
+        <v>0.6161616161616164</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.0002365505624592468</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.0002365505624592468</v>
       </c>
     </row>
     <row r="83">
@@ -1081,7 +1578,13 @@
         <v>0.6363636363636365</v>
       </c>
       <c r="B83" t="n">
-        <v>0.0002896805735329998</v>
+        <v>0.6363636363636365</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.000289678650274081</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.000289678650274081</v>
       </c>
     </row>
     <row r="84">
@@ -1089,7 +1592,13 @@
         <v>0.6565656565656568</v>
       </c>
       <c r="B84" t="n">
-        <v>0.000354620992086229</v>
+        <v>0.6565656565656568</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.0003545391275556278</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.0003545391275556278</v>
       </c>
     </row>
     <row r="85">
@@ -1097,7 +1606,13 @@
         <v>0.6767676767676769</v>
       </c>
       <c r="B85" t="n">
-        <v>0.0004340841647071061</v>
+        <v>0.6767676767676769</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.0004341405004539019</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.0004341405004539019</v>
       </c>
     </row>
     <row r="86">
@@ -1105,7 +1620,13 @@
         <v>0.696969696969697</v>
       </c>
       <c r="B86" t="n">
-        <v>0.0005314996849678932</v>
+        <v>0.696969696969697</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.0005315158904613432</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.0005315158904613432</v>
       </c>
     </row>
     <row r="87">
@@ -1113,7 +1634,13 @@
         <v>0.7171717171717173</v>
       </c>
       <c r="B87" t="n">
-        <v>0.0006504832084749676</v>
+        <v>0.7171717171717173</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.0006505471116252766</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.0006505471116252766</v>
       </c>
     </row>
     <row r="88">
@@ -1121,7 +1648,13 @@
         <v>0.7373737373737375</v>
       </c>
       <c r="B88" t="n">
-        <v>0.0007962254630512937</v>
+        <v>0.7373737373737375</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.0007962782855528133</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.0007962782855528133</v>
       </c>
     </row>
     <row r="89">
@@ -1129,7 +1662,13 @@
         <v>0.7575757575757578</v>
       </c>
       <c r="B89" t="n">
-        <v>0.0009746884037445674</v>
+        <v>0.7575757575757578</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.0009747460231809059</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.0009747460231809059</v>
       </c>
     </row>
     <row r="90">
@@ -1137,7 +1676,13 @@
         <v>0.7777777777777779</v>
       </c>
       <c r="B90" t="n">
-        <v>0.0011929930476819</v>
+        <v>0.7777777777777779</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.001192969464448897</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.001192969464448897</v>
       </c>
     </row>
     <row r="91">
@@ -1145,7 +1690,13 @@
         <v>0.7979797979797982</v>
       </c>
       <c r="B91" t="n">
-        <v>0.001460275308506377</v>
+        <v>0.7979797979797982</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.001460116944831034</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.001460116944831034</v>
       </c>
     </row>
     <row r="92">
@@ -1153,7 +1704,13 @@
         <v>0.8181818181818183</v>
       </c>
       <c r="B92" t="n">
-        <v>0.001787261370012793</v>
+        <v>0.8181818181818183</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.001787143597443976</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.001787143597443976</v>
       </c>
     </row>
     <row r="93">
@@ -1161,7 +1718,13 @@
         <v>0.8383838383838385</v>
       </c>
       <c r="B93" t="n">
-        <v>0.002187452013428648</v>
+        <v>0.8383838383838385</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.00218745094414892</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.00218745094414892</v>
       </c>
     </row>
     <row r="94">
@@ -1169,7 +1732,13 @@
         <v>0.8585858585858588</v>
       </c>
       <c r="B94" t="n">
-        <v>0.002677150586913445</v>
+        <v>0.8585858585858588</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.002677202856064383</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.002677202856064383</v>
       </c>
     </row>
     <row r="95">
@@ -1177,7 +1746,13 @@
         <v>0.8787878787878789</v>
       </c>
       <c r="B95" t="n">
-        <v>0.003276652528647134</v>
+        <v>0.8787878787878789</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.00327657181407154</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.00327657181407154</v>
       </c>
     </row>
     <row r="96">
@@ -1185,7 +1760,13 @@
         <v>0.8989898989898992</v>
       </c>
       <c r="B96" t="n">
-        <v>0.004010332390760075</v>
+        <v>0.8989898989898992</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.00401035435281988</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.00401035435281988</v>
       </c>
     </row>
     <row r="97">
@@ -1193,7 +1774,13 @@
         <v>0.9191919191919193</v>
       </c>
       <c r="B97" t="n">
-        <v>0.004908266829048363</v>
+        <v>0.9191919191919193</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.004908263983411564</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.004908263983411564</v>
       </c>
     </row>
     <row r="98">
@@ -1201,7 +1788,13 @@
         <v>0.9393939393939394</v>
       </c>
       <c r="B98" t="n">
-        <v>0.006007149278173167</v>
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.006007021025766734</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.006007021025766734</v>
       </c>
     </row>
     <row r="99">
@@ -1209,7 +1802,13 @@
         <v>0.9595959595959598</v>
       </c>
       <c r="B99" t="n">
-        <v>0.007352179730496839</v>
+        <v>0.9595959595959598</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.007352191686223238</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.007352191686223238</v>
       </c>
     </row>
     <row r="100">
@@ -1217,7 +1816,13 @@
         <v>0.9797979797979799</v>
       </c>
       <c r="B100" t="n">
-        <v>0.008998122974222329</v>
+        <v>0.9797979797979799</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.008998227037263128</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.008998227037263128</v>
       </c>
     </row>
     <row r="101">
@@ -1225,7 +1830,49 @@
         <v>1</v>
       </c>
       <c r="B101" t="n">
-        <v>0.01101274539731444</v>
+        <v>1</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.01101274912631012</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.01101274912631012</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha y hora inicio</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Isc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-02 10:00:00</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12.3</v>
       </c>
     </row>
   </sheetData>
